--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -514,6 +514,35 @@
         <v>46170.52393518519</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>46171.00479416666</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>46171.74891203704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -540,7 +540,7 @@
         <v>46171</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>46171.74891203704</v>
+        <v>46172.46280092592</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -543,6 +543,35 @@
         <v>46172.46280092592</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>46172.62657414352</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>46173.49481481482</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -572,6 +572,35 @@
         <v>46173.49481481482</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>46174.28626871528</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>46174.8787037037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -601,6 +601,35 @@
         <v>46174.8787037037</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>78.13</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>46175.00493798611</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>46175</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>46175.4562962963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -627,7 +627,7 @@
         <v>46175</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>46175.4562962963</v>
+        <v>46175.7933449074</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -630,6 +630,35 @@
         <v>46175.7933449074</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>46176.00505787037</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>46176</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>46176.31853009259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -656,7 +656,7 @@
         <v>46176</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>46176.31853009259</v>
+        <v>46176.83381944444</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -659,6 +659,35 @@
         <v>46176.83381944444</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>46177.00486586805</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>46177</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>46177.73150462963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -688,6 +688,35 @@
         <v>46177.73150462963</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>46178.00519586806</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>46178.67769675926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -714,7 +714,7 @@
         <v>46178</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>46178.67769675926</v>
+        <v>46179.46704861111</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -717,6 +717,35 @@
         <v>46179.46704861111</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>46179.91686961806</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>46179</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>46180.50591435185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -746,6 +746,35 @@
         <v>46180.50591435185</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>46181.26554702546</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>46181.73435185185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -775,6 +775,35 @@
         <v>46181.73435185185</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>75.91</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>46182.00506563657</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>46182</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>46182.68064814815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -804,6 +804,35 @@
         <v>46182.68064814815</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>75.13</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>46183.00486690972</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>46183</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>46183.73943287037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -833,6 +833,35 @@
         <v>46183.73943287037</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>46184.00482302083</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>46184</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>46184.74893518518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -862,6 +862,35 @@
         <v>46184.74893518518</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>46185.00501114583</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>46185.69063657407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -888,7 +888,7 @@
         <v>46185</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>46185.69063657407</v>
+        <v>46186.50677083333</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -891,6 +891,35 @@
         <v>46186.50677083333</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>46186.62669377315</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>46186</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>46187.5203587963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -920,6 +920,35 @@
         <v>46187.5203587963</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>46204.01583907408</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>46204.4122337963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -949,6 +949,35 @@
         <v>46204.4122337963</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>46205.00115108796</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>46205</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>46205.38689814815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -978,6 +978,35 @@
         <v>46205.38689814815</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>46206.00533894676</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>46206.39077546296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1007,6 +1007,35 @@
         <v>46206.39077546296</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>80.59</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>46207.11323087963</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>46207</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>46207.36204861111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -1033,7 +1033,7 @@
         <v>46207</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>46207.36204861111</v>
+        <v>46208.37267361111</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1036,6 +1036,35 @@
         <v>46208.37267361111</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>46209.26562596064</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>46209.4459375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1065,6 +1065,35 @@
         <v>46209.4459375</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>46210.00501899306</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>46210</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>46210.40768518519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1094,6 +1094,35 @@
         <v>46210.40768518519</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>80.19</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>46211.00670284723</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>46211</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>46211.35664351852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1123,6 +1123,35 @@
         <v>46211.35664351852</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>46213.26554664352</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>46213</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>46213.4027199074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -1149,7 +1149,7 @@
         <v>46213</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>46213.4027199074</v>
+        <v>46214.33351851852</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1152,6 +1152,35 @@
         <v>46214.33351851852</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>46214.73077037037</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>46214</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>46215.34836805556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1181,6 +1181,35 @@
         <v>46215.34836805556</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>78.87</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>46216.26465643518</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>46216</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>46216.39753472222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1210,6 +1210,35 @@
         <v>46216.39753472222</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>80.11</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>46217.00077309028</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>46217.34078703704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1239,6 +1239,35 @@
         <v>46217.34078703704</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>46218.00062998843</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>46218</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>46218.34556712963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,35 @@
         <v>46218.34556712963</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>81.16</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>46219.00085594907</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>46219.34600694444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1297,6 +1297,35 @@
         <v>46219.34600694444</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>46220.00119967593</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>46220</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>46220.34266203704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1326,6 +1326,35 @@
         <v>46220.34266203704</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>79.11</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>46221.00174430555</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>46221.33009259259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -1352,7 +1352,7 @@
         <v>46221</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>46221.33009259259</v>
+        <v>46222.34950231481</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1355,6 +1355,35 @@
         <v>46222.34950231481</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>46223.26488583333</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>46223.38840277777</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1384,6 +1384,35 @@
         <v>46223.38840277777</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>83.27</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>46224.00197572917</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>46224.35628472222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1413,6 +1413,35 @@
         <v>46224.35628472222</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>46225.00152371528</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>46225</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>46225.35609953704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1442,6 +1442,35 @@
         <v>46225.35609953704</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>46226.00190310185</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>46226</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>46226.35719907407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1471,6 +1471,35 @@
         <v>46226.35719907407</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>46227.00135366898</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>46227</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>46227.355625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1500,6 +1500,35 @@
         <v>46227.355625</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>46228.0707975</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>46228</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>46228.33993055556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -1526,7 +1526,7 @@
         <v>46228</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>46228.33993055556</v>
+        <v>46229.35428240741</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1529,6 +1529,35 @@
         <v>46229.35428240741</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>83.47</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>46230.26477398148</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>46230.41414351852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1558,6 +1558,35 @@
         <v>46230.41414351852</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>82.33</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>46231.00462559028</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>46231</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>46231.3596875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1587,6 +1587,35 @@
         <v>46231.3596875</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>46232.00496688658</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>46232.36436342593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1616,6 +1616,35 @@
         <v>46232.36436342593</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>46233.00466777778</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>46233</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>46233.3544675926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1645,6 +1645,35 @@
         <v>46233.3544675926</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>46235.00442625</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>46235.35012731481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -1671,7 +1671,7 @@
         <v>46235</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>46235.35012731481</v>
+        <v>46236.3521875</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1674,6 +1674,35 @@
         <v>46236.3521875</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>46237.26181983796</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>46237</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>46237.41011574074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1703,6 +1703,35 @@
         <v>46237.41011574074</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>46238.00125269676</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>46238.36159722223</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1732,6 +1732,35 @@
         <v>46238.36159722223</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>81.34</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>46239.00365665509</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>46239.36071759259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1761,35 @@
         <v>46239.36071759259</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>81.09</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>46240.0046965625</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>46240.36127314815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1790,6 +1790,35 @@
         <v>46240.36127314815</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>46241.00134418981</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>46241.30521990741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -1816,7 +1816,7 @@
         <v>46241</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>46241.30521990741</v>
+        <v>46242.28942129629</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1819,6 +1819,35 @@
         <v>46242.28942129629</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>83.29000000000001</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>46242.66559597222</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>46242</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>46243.29165509259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1848,6 +1848,35 @@
         <v>46243.29165509259</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>46244.26516040509</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>46244.32335648148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1877,6 +1877,35 @@
         <v>46244.32335648148</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>46245.00065665509</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>46245.29971064815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1906,6 +1906,35 @@
         <v>46245.29971064815</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>46246.0881539699</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>46246.31081018518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1935,6 +1935,35 @@
         <v>46246.31081018518</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>46247.00451278935</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>46247.31789351852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1964,6 +1964,35 @@
         <v>46247.31789351852</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>46248.004160625</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>46248.31060185185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1993,6 +1993,35 @@
         <v>46248.31060185185</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>46249.01139172454</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>46249</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>46249.27853009259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2019,7 +2019,7 @@
         <v>46249</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>46249.27853009259</v>
+        <v>46250.27932870371</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2022,6 +2022,35 @@
         <v>46250.27932870371</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>81.86</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>46251.26170134259</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>46251.29130787037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2051,6 +2051,35 @@
         <v>46251.29130787037</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>46252.00439841435</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>46252</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>46252.28262731482</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2080,35 @@
         <v>46252.28262731482</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>82.31</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>46253.00128733796</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>46253.28328703704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2109,6 +2109,35 @@
         <v>46253.28328703704</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>46254.00150732639</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>46254.28488425926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2138,6 +2138,35 @@
         <v>46254.28488425926</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>46255.00469755787</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>46255.28543981481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2167,35 @@
         <v>46255.28543981481</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>46256.01152613426</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>46256</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>46256.27956018518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2193,7 +2193,7 @@
         <v>46256</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>46256.27956018518</v>
+        <v>46257.2806712963</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2196,6 +2196,35 @@
         <v>46257.2806712963</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>46258.26487450232</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>46258.29325231481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2225,6 +2225,35 @@
         <v>46258.29325231481</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>46259.00109766204</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>46259.2862962963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2254,6 +2254,35 @@
         <v>46259.2862962963</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>46260.03638938657</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>46260.28710648148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2283,6 +2283,35 @@
         <v>46260.28710648148</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>46261.00157521991</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>46261.72688657408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2312,6 +2312,35 @@
         <v>46261.72688657408</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>46262.00481252315</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>46262.76392361111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2338,7 +2338,7 @@
         <v>46262</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>46262.76392361111</v>
+        <v>46263.51987268519</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2341,6 +2341,35 @@
         <v>46263.51987268519</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>82.73</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>46263.66575116898</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>46264.47921296296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2370,6 +2370,35 @@
         <v>46264.47921296296</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>82.79000000000001</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>46265.26494013889</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>46265.54331018519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2399,6 +2399,35 @@
         <v>46265.54331018519</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>46266.00463510417</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>46266.47134259259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2428,6 +2428,35 @@
         <v>46266.47134259259</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>83.34</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>46267.00475767361</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>46267</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>46267.45340277778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2457,6 +2457,35 @@
         <v>46267.45340277778</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>46268.00476089121</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>46268.45318287037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2483,7 +2483,7 @@
         <v>46268</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>46268.45318287037</v>
+        <v>46269.45268518518</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2486,6 +2486,35 @@
         <v>46269.45268518518</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>84.18000000000001</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>46270.01855166667</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>46270.42408564815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2512,7 +2512,7 @@
         <v>46270</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>46270.42408564815</v>
+        <v>46271.43847222222</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -2512,7 +2512,7 @@
         <v>46270</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>46271.43847222222</v>
+        <v>46272.4962037037</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2515,6 +2515,35 @@
         <v>46272.4962037037</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>46273.00446354166</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>46273.45209490741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2544,6 +2544,35 @@
         <v>46273.45209490741</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>85.42</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>46274.00150206019</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>46274.45605324074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2573,6 +2573,35 @@
         <v>46274.45605324074</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>46275.00132055556</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>46275</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>46275.45363425926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2602,6 +2602,35 @@
         <v>46275.45363425926</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>46276.00473520833</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>46276.45151620371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_EUAs_Price.xlsx
+++ b/Historico_EUAs_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2631,6 +2631,35 @@
         <v>46276.45151620371</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>46277.00117004629</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>46277</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>46277.42946759259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
